--- a/feedback_forms/040_doctor_bedside_manner_feedback_form--feedback_forms.xlsx
+++ b/feedback_forms/040_doctor_bedside_manner_feedback_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1033,8 +1033,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'option1':_'just_the_right_amount'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'option1': 'Just the right amount'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'option2':_'a_little_too_little'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'option2': 'A little too little'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'option3':_'a_lot_too_much'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'option3': 'A lot too much'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1895,12 +1895,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1963,12 +1963,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2014,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2031,12 +2031,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2065,12 +2065,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2082,12 +2082,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2116,12 +2116,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'option1':_'excellent'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'option1': 'Excellent'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'option2':_'good'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'option2': 'Good'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2167,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'option3':_'fair'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'option3': 'Fair'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2184,12 +2184,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'option4':_'bad'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'option4': 'Bad'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2201,12 +2201,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'option1':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'option1': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'option2':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'option2': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
